--- a/data/processed/positivacao/2023-01_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-01_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25413,7 +25413,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B965" t="inlineStr"/>
@@ -36843,7 +36843,7 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr"/>
@@ -65891,7 +65891,7 @@
     <row r="2523">
       <c r="A2523" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2523" t="inlineStr"/>
@@ -67562,12 +67562,12 @@
       <c r="A2588" t="inlineStr"/>
       <c r="B2588" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 9 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 37.228,70
+          <t>Vendedor 1 - VENDEDOR 01: positivou 9 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 37.228,70
 Vendedor 18 - LOJA: positivou 122 cliente(s), não positivou 736 cliente(s) - Total vendido: R$ 76.085,14
-Vendedor 3 - FERNANDA: positivou 109 cliente(s), não positivou 330 cliente(s) - Total vendido: R$ 156.901,35
-Vendedor 4 - DANIELA: positivou 64 cliente(s), não positivou 602 cliente(s) - Total vendido: R$ 38.924,18
+Vendedor 3 - VENDEDOR 03: positivou 109 cliente(s), não positivou 330 cliente(s) - Total vendido: R$ 156.901,35
+Vendedor 4 - VENDEDOR 04: positivou 64 cliente(s), não positivou 602 cliente(s) - Total vendido: R$ 38.924,18
 Vendedor 5 - SITE: positivou 6 cliente(s), não positivou 444 cliente(s) - Total vendido: R$ 482,80
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2588" t="inlineStr"/>
